--- a/inspection_forms/028_dot_inspection_form--inspection_forms.xlsx
+++ b/inspection_forms/028_dot_inspection_form--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'ford',_'label':_'ford'}</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Ford', 'label': 'Ford'}</t>
+          <t>Ford</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'toyota',_'label':_'toyota'}</t>
+          <t>toyota</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Toyota', 'label': 'Toyota'}</t>
+          <t>Toyota</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'honda',_'label':_'honda'}</t>
+          <t>honda</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Honda', 'label': 'Honda'}</t>
+          <t>Honda</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'ford_f-150',_'label':_'ford_f-150'}</t>
+          <t>ford_f-150</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Ford F-150', 'label': 'Ford F-150'}</t>
+          <t>Ford F-150</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'toyota_corolla',_'label':_'toyota_corolla'}</t>
+          <t>toyota_corolla</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Toyota Corolla', 'label': 'Toyota Corolla'}</t>
+          <t>Toyota Corolla</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'honda_civic',_'label':_'honda_civic'}</t>
+          <t>honda_civic</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Honda Civic', 'label': 'Honda Civic'}</t>
+          <t>Honda Civic</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_2010,_'label':_2010}</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 2010, 'label': 2010}</t>
+          <t>2010</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_2015,_'label':_2015}</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 2015, 'label': 2015}</t>
+          <t>2015</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_2020,_'label':_2020}</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 2020, 'label': 2020}</t>
+          <t>2020</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'red',_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Red', 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'blue',_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Blue', 'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'green',_'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Green', 'label': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'car',_'label':_'car'}</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Car', 'label': 'Car'}</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'motorcycle',_'label':_'motorcycle'}</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Motorcycle', 'label': 'Motorcycle'}</t>
+          <t>Motorcycle</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'bicycle',_'label':_'bicycle'}</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Bicycle', 'label': 'Bicycle'}</t>
+          <t>Bicycle</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'safety',_'label':_'safety'}</t>
+          <t>safety</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Safety', 'label': 'Safety'}</t>
+          <t>Safety</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'emissions',_'label':_'emissions'}</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Emissions', 'label': 'Emissions'}</t>
+          <t>Emissions</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'maintenance',_'label':_'maintenance'}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Maintenance', 'label': 'Maintenance'}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
